--- a/docs/handouts/chapter_3_4_handout.xlsx
+++ b/docs/handouts/chapter_3_4_handout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RData\BYUI-Timeseries-Drafts\handouts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\craigaj\Documents\GitHub\timeseries\handouts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02469407-9672-40BC-AB1C-8C5870E59D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF78833-DEC7-4231-A69C-CE58C42B22AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{CB73943A-C465-40BE-817C-B9991112161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Workbook" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="44">
   <si>
     <t>t</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>_____</t>
   </si>
   <si>
     <t>2016 Q1</t>
@@ -215,7 +212,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +222,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -317,31 +320,35 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
       <right style="medium">
         <color theme="1"/>
@@ -349,76 +356,96 @@
       <top style="medium">
         <color theme="1"/>
       </top>
-      <bottom/>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
+      <bottom style="hair">
+        <color theme="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
-      <top/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="hair">
+        <color theme="1"/>
       </right>
-      <top/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="hair">
+        <color theme="1"/>
       </left>
       <right style="medium">
         <color theme="1"/>
       </right>
-      <top/>
+      <top style="hair">
+        <color theme="1"/>
+      </top>
       <bottom style="medium">
         <color theme="1"/>
       </bottom>
@@ -428,17 +455,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -471,13 +489,31 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -562,8 +598,8 @@
       <xdr:rowOff>53213</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -608,10 +644,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -645,7 +678,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="11" name="TextBox 10">
@@ -820,8 +853,8 @@
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="202298" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -866,10 +899,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -903,7 +933,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="10" name="TextBox 9">
@@ -968,8 +998,8 @@
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="193322" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -1014,10 +1044,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1051,7 +1078,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="17" name="TextBox 16">
@@ -1171,8 +1198,8 @@
       <xdr:rowOff>45593</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="180819" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -1217,10 +1244,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1254,7 +1278,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -1319,8 +1343,8 @@
       <xdr:rowOff>68453</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="196079" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1365,10 +1389,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -1414,7 +1435,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="TextBox 2">
@@ -1853,959 +1874,887 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABFF2E6-1E13-48EF-9BE3-D6C90C46BEC8}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.90625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.90625" customWidth="1"/>
+    <col min="10" max="10" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="48.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="48.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="21"/>
+    </row>
+    <row r="2" spans="1:7" ht="30.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="8">
+        <v>-3</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B4" s="11">
+        <v>-2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="11">
+        <v>-1000</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="11">
+        <v>-1</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="11">
+        <v>-1000</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="11">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1990</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="11">
+        <v>2</v>
+      </c>
+      <c r="C8" s="11">
+        <v>603</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="11">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11">
+        <v>326</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="11">
+        <v>4</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1495</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="11">
+        <v>5</v>
+      </c>
+      <c r="C11" s="11">
+        <v>2331</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1508</v>
+      </c>
+      <c r="E11" s="11">
+        <v>-58</v>
+      </c>
+      <c r="F11" s="11">
+        <v>805</v>
+      </c>
+      <c r="G11" s="12">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="11">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11">
+        <v>729</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1519</v>
+      </c>
+      <c r="E12" s="11">
+        <v>-44</v>
+      </c>
+      <c r="F12" s="11">
+        <v>-1012</v>
+      </c>
+      <c r="G12" s="12">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="11">
+        <v>7</v>
+      </c>
+      <c r="C13" s="11">
+        <v>318</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1464</v>
+      </c>
+      <c r="E13" s="11">
+        <v>-46</v>
+      </c>
+      <c r="F13" s="11">
+        <v>-1110</v>
+      </c>
+      <c r="G13" s="12">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="11">
+        <v>8</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1620</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1301</v>
+      </c>
+      <c r="E14" s="11">
+        <v>-69</v>
+      </c>
+      <c r="F14" s="11">
+        <v>693</v>
+      </c>
+      <c r="G14" s="12">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="11">
+        <v>9</v>
+      </c>
+      <c r="C15" s="11">
+        <v>2451</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1315</v>
+      </c>
+      <c r="E15" s="11">
+        <v>-52</v>
+      </c>
+      <c r="F15" s="11">
+        <v>871</v>
+      </c>
+      <c r="G15" s="12">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="11">
+        <v>10</v>
+      </c>
+      <c r="C16" s="11">
+        <v>670</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1347</v>
+      </c>
+      <c r="E16" s="11">
+        <v>-35</v>
+      </c>
+      <c r="F16" s="11">
+        <v>-945</v>
+      </c>
+      <c r="G16" s="12">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="11">
+        <v>11</v>
+      </c>
+      <c r="C17" s="11">
+        <v>323</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1336</v>
+      </c>
+      <c r="E17" s="11">
+        <v>-30</v>
+      </c>
+      <c r="F17" s="11">
+        <v>-1091</v>
+      </c>
+      <c r="G17" s="12">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="11">
+        <v>12</v>
+      </c>
+      <c r="C18" s="11">
+        <v>1573</v>
+      </c>
+      <c r="D18" s="11">
+        <v>1221</v>
+      </c>
+      <c r="E18" s="11">
+        <v>-47</v>
+      </c>
+      <c r="F18" s="11">
+        <v>625</v>
+      </c>
+      <c r="G18" s="12">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="11">
+        <v>13</v>
+      </c>
+      <c r="C19" s="11">
+        <v>2089</v>
+      </c>
+      <c r="D19" s="11">
+        <v>1183</v>
+      </c>
+      <c r="E19" s="11">
+        <v>-45</v>
+      </c>
+      <c r="F19" s="11">
+        <v>878</v>
+      </c>
+      <c r="G19" s="12">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="11">
+        <v>14</v>
+      </c>
+      <c r="C20" s="11">
+        <v>751</v>
+      </c>
+      <c r="D20" s="11">
+        <v>1250</v>
+      </c>
+      <c r="E20" s="11">
+        <v>-23</v>
+      </c>
+      <c r="F20" s="11">
+        <v>-856</v>
+      </c>
+      <c r="G20" s="12">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="11">
+        <v>15</v>
+      </c>
+      <c r="C21" s="11">
+        <v>354</v>
+      </c>
+      <c r="D21" s="11">
+        <v>1271</v>
+      </c>
+      <c r="E21" s="11">
+        <v>-14</v>
+      </c>
+      <c r="F21" s="11">
+        <v>-1056</v>
+      </c>
+      <c r="G21" s="12">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="11">
+        <v>16</v>
+      </c>
+      <c r="C22" s="11">
+        <v>1481</v>
+      </c>
+      <c r="D22" s="11">
+        <v>1177</v>
+      </c>
+      <c r="E22" s="11">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="11">
+        <v>561</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="11">
+        <v>17</v>
+      </c>
+      <c r="C23" s="11">
+        <v>2345</v>
+      </c>
+      <c r="D23" s="11">
+        <v>1211</v>
+      </c>
+      <c r="E23" s="11">
+        <v>-17</v>
+      </c>
+      <c r="F23" s="11">
+        <v>929</v>
+      </c>
+      <c r="G23" s="12">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="11">
+        <v>18</v>
+      </c>
+      <c r="C24" s="11">
+        <v>690</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1264</v>
+      </c>
+      <c r="E24" s="11">
         <v>-3</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="11">
-        <v>1000</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="F24" s="11">
+        <v>-800</v>
+      </c>
+      <c r="G24" s="12">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="11">
+        <v>19</v>
+      </c>
+      <c r="C25" s="11">
+        <v>338</v>
+      </c>
+      <c r="D25" s="11">
+        <v>1288</v>
+      </c>
+      <c r="E25" s="11">
+        <v>2</v>
+      </c>
+      <c r="F25" s="11">
+        <v>-1035</v>
+      </c>
+      <c r="G25" s="12">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="11">
+        <v>20</v>
+      </c>
+      <c r="C26" s="11">
+        <v>1344</v>
+      </c>
+      <c r="D26" s="11">
+        <v>1189</v>
+      </c>
+      <c r="E26" s="11">
+        <v>-18</v>
+      </c>
+      <c r="F26" s="11">
+        <v>480</v>
+      </c>
+      <c r="G26" s="12">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="11">
+        <v>21</v>
+      </c>
+      <c r="C27" s="11">
+        <v>2337</v>
+      </c>
+      <c r="D27" s="11">
+        <v>1218</v>
+      </c>
+      <c r="E27" s="11">
+        <v>-9</v>
+      </c>
+      <c r="F27" s="11">
+        <v>967</v>
+      </c>
+      <c r="G27" s="12">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="11">
+        <v>22</v>
+      </c>
+      <c r="C28" s="11">
+        <v>710</v>
+      </c>
+      <c r="D28" s="11">
+        <v>1269</v>
+      </c>
+      <c r="E28" s="11">
+        <v>3</v>
+      </c>
+      <c r="F28" s="11">
+        <v>-752</v>
+      </c>
+      <c r="G28" s="12">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" s="11">
+        <v>23</v>
+      </c>
+      <c r="C29" s="11">
+        <v>327</v>
+      </c>
+      <c r="D29" s="11">
+        <v>1290</v>
+      </c>
+      <c r="E29" s="11">
+        <v>7</v>
+      </c>
+      <c r="F29" s="11">
+        <v>-1021</v>
+      </c>
+      <c r="G29" s="12">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="11">
+        <v>24</v>
+      </c>
+      <c r="C30" s="11">
+        <v>1590</v>
+      </c>
+      <c r="D30" s="11">
+        <v>1260</v>
+      </c>
+      <c r="E30" s="11">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11">
+        <v>450</v>
+      </c>
+      <c r="G30" s="12">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="11">
+        <v>25</v>
+      </c>
+      <c r="C31" s="11">
+        <v>2115</v>
+      </c>
+      <c r="D31" s="11">
+        <v>1238</v>
+      </c>
+      <c r="E31" s="11">
+        <v>-4</v>
+      </c>
+      <c r="F31" s="11">
+        <v>949</v>
+      </c>
+      <c r="G31" s="12">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="11">
+        <v>26</v>
+      </c>
+      <c r="C32" s="11">
+        <v>663</v>
+      </c>
+      <c r="D32" s="11">
+        <v>1270</v>
+      </c>
+      <c r="E32" s="11">
+        <v>3</v>
+      </c>
+      <c r="F32" s="11">
+        <v>-723</v>
+      </c>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="11">
+        <v>27</v>
+      </c>
+      <c r="C33" s="11">
+        <v>329</v>
+      </c>
+      <c r="D33" s="11">
+        <v>1288</v>
+      </c>
+      <c r="E33" s="11">
         <v>6</v>
       </c>
-      <c r="B4" s="14">
-        <v>-2</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="14">
-        <v>-1000</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="14">
-        <v>-1</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="14">
-        <v>-1000</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14">
-        <v>0</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="14">
-        <v>1000</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14">
-        <v>1990</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="14">
-        <v>2</v>
-      </c>
-      <c r="C8" s="14">
-        <v>603</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="14">
-        <v>3</v>
-      </c>
-      <c r="C9" s="14">
-        <v>326</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="14">
-        <v>4</v>
-      </c>
-      <c r="C10" s="14">
-        <v>1495</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="14">
-        <v>5</v>
-      </c>
-      <c r="C11" s="14">
-        <v>2331</v>
-      </c>
-      <c r="D11" s="14">
-        <v>1508</v>
-      </c>
-      <c r="E11" s="14">
-        <v>-58</v>
-      </c>
-      <c r="F11" s="14">
-        <v>805</v>
-      </c>
-      <c r="G11" s="15">
-        <v>2313</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="14">
-        <v>6</v>
-      </c>
-      <c r="C12" s="14">
-        <v>729</v>
-      </c>
-      <c r="D12" s="14">
-        <v>1519</v>
-      </c>
-      <c r="E12" s="14">
-        <v>-44</v>
-      </c>
-      <c r="F12" s="14">
-        <v>-1012</v>
-      </c>
-      <c r="G12" s="15">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="14">
-        <v>7</v>
-      </c>
-      <c r="C13" s="14">
-        <v>318</v>
-      </c>
-      <c r="D13" s="14">
-        <v>1464</v>
-      </c>
-      <c r="E13" s="14">
-        <v>-46</v>
-      </c>
-      <c r="F13" s="14">
-        <v>-1110</v>
-      </c>
-      <c r="G13" s="15">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="14">
-        <v>8</v>
-      </c>
-      <c r="C14" s="14">
-        <v>1620</v>
-      </c>
-      <c r="D14" s="14">
-        <v>1301</v>
-      </c>
-      <c r="E14" s="14">
-        <v>-69</v>
-      </c>
-      <c r="F14" s="14">
-        <v>693</v>
-      </c>
-      <c r="G14" s="15">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="14">
-        <v>9</v>
-      </c>
-      <c r="C15" s="14">
-        <v>2451</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1315</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-52</v>
-      </c>
-      <c r="F15" s="14">
-        <v>871</v>
-      </c>
-      <c r="G15" s="15">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="14">
-        <v>10</v>
-      </c>
-      <c r="C16" s="14">
-        <v>670</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1347</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-35</v>
-      </c>
-      <c r="F16" s="14">
-        <v>-945</v>
-      </c>
-      <c r="G16" s="15">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="14">
-        <v>11</v>
-      </c>
-      <c r="C17" s="14">
-        <v>323</v>
-      </c>
-      <c r="D17" s="14">
-        <v>1336</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-30</v>
-      </c>
-      <c r="F17" s="14">
-        <v>-1091</v>
-      </c>
-      <c r="G17" s="15">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="14">
-        <v>12</v>
-      </c>
-      <c r="C18" s="14">
-        <v>1573</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1221</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-47</v>
-      </c>
-      <c r="F18" s="14">
-        <v>625</v>
-      </c>
-      <c r="G18" s="15">
-        <v>1846</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="14">
-        <v>13</v>
-      </c>
-      <c r="C19" s="14">
-        <v>2089</v>
-      </c>
-      <c r="D19" s="14">
-        <v>1183</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-45</v>
-      </c>
-      <c r="F19" s="14">
-        <v>878</v>
-      </c>
-      <c r="G19" s="15">
-        <v>2061</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="14">
-        <v>14</v>
-      </c>
-      <c r="C20" s="14">
-        <v>751</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1250</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-23</v>
-      </c>
-      <c r="F20" s="14">
-        <v>-856</v>
-      </c>
-      <c r="G20" s="15">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="14">
-        <v>15</v>
-      </c>
-      <c r="C21" s="14">
-        <v>354</v>
-      </c>
-      <c r="D21" s="14">
-        <v>1271</v>
-      </c>
-      <c r="E21" s="14">
-        <v>-14</v>
-      </c>
-      <c r="F21" s="14">
-        <v>-1056</v>
-      </c>
-      <c r="G21" s="15">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="14">
-        <v>16</v>
-      </c>
-      <c r="C22" s="14">
-        <v>1481</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1177</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-30</v>
-      </c>
-      <c r="F22" s="14">
-        <v>561</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1738</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="14">
-        <v>17</v>
-      </c>
-      <c r="C23" s="14">
-        <v>2345</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1211</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-17</v>
-      </c>
-      <c r="F23" s="14">
-        <v>929</v>
-      </c>
-      <c r="G23" s="15">
-        <v>2140</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="14">
-        <v>18</v>
-      </c>
-      <c r="C24" s="14">
-        <v>690</v>
-      </c>
-      <c r="D24" s="14">
-        <v>1264</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-3</v>
-      </c>
-      <c r="F24" s="14">
-        <v>-800</v>
-      </c>
-      <c r="G24" s="15">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="14">
-        <v>19</v>
-      </c>
-      <c r="C25" s="14">
-        <v>338</v>
-      </c>
-      <c r="D25" s="14">
-        <v>1288</v>
-      </c>
-      <c r="E25" s="14">
-        <v>2</v>
-      </c>
-      <c r="F25" s="14">
-        <v>-1035</v>
-      </c>
-      <c r="G25" s="15">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+      <c r="F33" s="11">
+        <v>-1021</v>
+      </c>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="11">
         <v>28</v>
       </c>
-      <c r="B26" s="14">
-        <v>20</v>
-      </c>
-      <c r="C26" s="14">
-        <v>1344</v>
-      </c>
-      <c r="D26" s="14">
-        <v>1189</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-18</v>
-      </c>
-      <c r="F26" s="14">
-        <v>480</v>
-      </c>
-      <c r="G26" s="15">
-        <v>1669</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
+      <c r="C34" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="13"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="11">
         <v>29</v>
       </c>
-      <c r="B27" s="14">
-        <v>21</v>
-      </c>
-      <c r="C27" s="14">
-        <v>2337</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1218</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-9</v>
-      </c>
-      <c r="F27" s="14">
-        <v>967</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2185</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+      <c r="C35" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="13"/>
+      <c r="G35" s="14"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="11">
         <v>30</v>
       </c>
-      <c r="B28" s="14">
-        <v>22</v>
-      </c>
-      <c r="C28" s="14">
-        <v>710</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1269</v>
-      </c>
-      <c r="E28" s="14">
-        <v>3</v>
-      </c>
-      <c r="F28" s="14">
-        <v>-752</v>
-      </c>
-      <c r="G28" s="15">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
+      <c r="C36" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="13"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="11">
         <v>31</v>
       </c>
-      <c r="B29" s="14">
-        <v>23</v>
-      </c>
-      <c r="C29" s="14">
-        <v>327</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1290</v>
-      </c>
-      <c r="E29" s="14">
-        <v>7</v>
-      </c>
-      <c r="F29" s="14">
-        <v>-1021</v>
-      </c>
-      <c r="G29" s="15">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+      <c r="C37" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="11">
         <v>32</v>
       </c>
-      <c r="B30" s="14">
-        <v>24</v>
-      </c>
-      <c r="C30" s="14">
-        <v>1590</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1260</v>
-      </c>
-      <c r="E30" s="14">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>450</v>
-      </c>
-      <c r="G30" s="15">
-        <v>1710</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
+      <c r="C38" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="13"/>
+      <c r="G38" s="14"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="11">
         <v>33</v>
       </c>
-      <c r="B31" s="14">
-        <v>25</v>
-      </c>
-      <c r="C31" s="14">
-        <v>2115</v>
-      </c>
-      <c r="D31" s="14">
-        <v>1238</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-4</v>
-      </c>
-      <c r="F31" s="14">
-        <v>949</v>
-      </c>
-      <c r="G31" s="15">
-        <v>2187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+      <c r="C39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" s="13"/>
+      <c r="G39" s="14"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="11">
         <v>34</v>
       </c>
-      <c r="B32" s="14">
-        <v>26</v>
-      </c>
-      <c r="C32" s="14">
-        <v>663</v>
-      </c>
-      <c r="D32" s="14">
-        <v>1270</v>
-      </c>
-      <c r="E32" s="14">
-        <v>3</v>
-      </c>
-      <c r="F32" s="14">
-        <v>-723</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
+      <c r="C40" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="13"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="11">
         <v>35</v>
       </c>
-      <c r="B33" s="14">
-        <v>27</v>
-      </c>
-      <c r="C33" s="14">
-        <v>329</v>
-      </c>
-      <c r="D33" s="14">
-        <v>1288</v>
-      </c>
-      <c r="E33" s="14">
-        <v>6</v>
-      </c>
-      <c r="F33" s="14">
-        <v>-1021</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
+      <c r="C41" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="13"/>
+      <c r="G41" s="14"/>
+    </row>
+    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="16">
         <v>36</v>
       </c>
-      <c r="B34" s="14">
-        <v>28</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="14">
-        <v>29</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="14">
-        <v>30</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="14">
-        <v>31</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="14">
-        <v>32</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="14">
-        <v>33</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="14">
-        <v>34</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="14">
-        <v>35</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="17">
-        <v>36</v>
-      </c>
-      <c r="C42" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>4</v>
-      </c>
+      <c r="C42" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="17"/>
+      <c r="G42" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2818,15 +2767,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_activity xmlns="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xsi:nil="true"/>
@@ -2834,7 +2774,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010070F75838E79B0E48B83E8E3F5479A3A2" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2b0c304636f8f537543cd13f583db9d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="ca1cba85-b018-40b2-9d9a-243cd5b6fae5" xmlns:ns4="f1fb8133-dfcb-4ab3-83e1-bcafde3f766a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f089f22c5ce4e61126931f7622145b2" ns3:_="" ns4:_="">
     <xsd:import namespace="ca1cba85-b018-40b2-9d9a-243cd5b6fae5"/>
@@ -3029,15 +2969,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E1B631-90B0-4D19-A35E-F8DC8BE167A4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3054,7 +2995,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBDDC771-C014-4A48-9FCA-802C556EA1D0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3071,4 +3012,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C96E0334-A0AA-41B5-AE21-CAD1C9D10746}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>